--- a/spreadsheet_demos/mods_default_tiff_images_validation_examples.xlsx
+++ b/spreadsheet_demos/mods_default_tiff_images_validation_examples.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>imageAccessibilityAltText</t>
+          <t>noteImageAltText</t>
         </is>
       </c>
     </row>
